--- a/data/trans_camb/P32C-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,11</t>
+          <t>-2,27; 1,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,78</t>
+          <t>-0,87; 3,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,97</t>
+          <t>-1,12; 4,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,0</t>
+          <t>-6,08; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,81</t>
+          <t>-4,92; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,83</t>
+          <t>-4,36; 1,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,3</t>
+          <t>-2,54; 0,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,45</t>
+          <t>-1,1; 2,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,1</t>
+          <t>-0,98; 2,98</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-72,61; 74,52</t>
+          <t>-68,3; 89,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 235,27</t>
+          <t>-30,66; 266,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 231,78</t>
+          <t>-38,06; 264,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,68; 35,53</t>
+          <t>-78,6; 38,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 152,84</t>
+          <t>-41,51; 172,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,58; 186,06</t>
+          <t>-36,0; 206,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,52</t>
+          <t>-0,82; 1,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,55</t>
+          <t>-1,46; 0,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; -0,08</t>
+          <t>-1,96; -0,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,65</t>
+          <t>-1,34; 0,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,65</t>
+          <t>-1,17; 0,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,85</t>
+          <t>-0,87; 1,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,94</t>
+          <t>-0,65; 0,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,33</t>
+          <t>-1,08; 0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,32</t>
+          <t>-1,25; 0,37</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 141,68</t>
+          <t>-39,03; 145,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,02; 64,26</t>
+          <t>-64,46; 48,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,1; 6,63</t>
+          <t>-83,45; 13,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 306,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 308,73</t>
+          <t>-88,41; 348,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 741,98</t>
+          <t>-75,58; 517,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 104,14</t>
+          <t>-38,17; 116,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 39,42</t>
+          <t>-62,01; 54,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,89; 41,27</t>
+          <t>-68,97; 44,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,24</t>
+          <t>-2,0; 3,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,98</t>
+          <t>-2,85; 0,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,52</t>
+          <t>-2,95; 0,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,0</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,66</t>
+          <t>-2,1; 0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,39</t>
+          <t>-2,14; 0,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,57</t>
+          <t>-1,53; 1,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,37</t>
+          <t>-2,13; 0,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,2</t>
+          <t>-2,27; 0,18</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 389,38</t>
+          <t>-73,38; 369,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,08; 124,92</t>
+          <t>-89,34; 112,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-92,44; 81,21</t>
+          <t>-93,11; 73,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 217,57</t>
+          <t>-78,99; 230,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 67,29</t>
+          <t>-90,33; 90,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-92,77; 48,34</t>
+          <t>-92,47; 57,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,87</t>
+          <t>-0,77; 0,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,58</t>
+          <t>-1,08; 0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,08</t>
+          <t>-1,42; 0,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,03</t>
+          <t>-1,47; 0,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,4</t>
+          <t>-1,32; 0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,06</t>
+          <t>-1,05; 0,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,44</t>
+          <t>-0,8; 0,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,3</t>
+          <t>-0,92; 0,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,11</t>
+          <t>-1,09; 0,16</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 57,81</t>
+          <t>-35,35; 64,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,97; 40,27</t>
+          <t>-47,05; 37,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 8,54</t>
+          <t>-63,39; 8,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,9</t>
+          <t>-100,0; 49,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,0; 117,35</t>
+          <t>-84,19; 148,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 223,03</t>
+          <t>-73,62; 194,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,04; 34,94</t>
+          <t>-41,15; 45,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,34; 23,65</t>
+          <t>-48,64; 34,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,32; 10,5</t>
+          <t>-58,93; 11,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32C-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32C-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,19</t>
+          <t>-2,28; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,97</t>
+          <t>-0,9; 3,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,08</t>
+          <t>-1,22; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,0</t>
+          <t>-6,44; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,95</t>
+          <t>-5,31; 0,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 1,96</t>
+          <t>-4,75; 1,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,42</t>
+          <t>-2,49; 0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,85</t>
+          <t>-1,1; 2,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,98</t>
+          <t>-1,22; 2,88</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-31,79%</t>
+          <t>-36,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,3; 89,52</t>
+          <t>-69,38; 96,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 266,33</t>
+          <t>-33,55; 217,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 264,61</t>
+          <t>-37,23; 236,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,6; 38,89</t>
+          <t>-76,45; 31,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 172,53</t>
+          <t>-37,97; 205,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 206,07</t>
+          <t>-42,7; 180,98</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,46</t>
+          <t>-0,74; 1,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,48</t>
+          <t>-1,48; 0,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; -0,04</t>
+          <t>-1,97; -0,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,65</t>
+          <t>-1,35; 0,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,66</t>
+          <t>-1,28; 0,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,73</t>
+          <t>-0,24; 3,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,95</t>
+          <t>-0,59; 1,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,42</t>
+          <t>-1,05; 0,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,37</t>
+          <t>-1,04; 0,68</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-56,89%</t>
+          <t>-58,12%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>139,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,27%</t>
+          <t>-18,84%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 145,2</t>
+          <t>-34,32; 131,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 48,15</t>
+          <t>-65,21; 55,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,45; 13,45</t>
+          <t>-85,95; -5,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 306,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,41; 348,47</t>
+          <t>-89,66; 288,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,58; 517,8</t>
+          <t>-47,21; 1048,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 116,86</t>
+          <t>-36,36; 113,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 54,89</t>
+          <t>-59,67; 48,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 44,42</t>
+          <t>-59,3; 75,02</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,08</t>
+          <t>-1,84; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,67</t>
+          <t>-2,74; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,34</t>
+          <t>-2,78; 0,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,67</t>
+          <t>-2,08; 0,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,4</t>
+          <t>-2,11; 0,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,6</t>
+          <t>-1,64; 1,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,42</t>
+          <t>-1,99; 0,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,18</t>
+          <t>-2,21; 0,26</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-56,9%</t>
+          <t>-49,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-61,41%</t>
+          <t>-61,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-60,17%</t>
+          <t>-54,74%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 369,05</t>
+          <t>-72,84; 333,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,34; 112,09</t>
+          <t>-89,97; 155,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,11; 73,52</t>
+          <t>-89,03; 160,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-78,99; 230,69</t>
+          <t>-84,78; 226,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,33; 90,2</t>
+          <t>-87,33; 78,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-92,47; 57,29</t>
+          <t>-88,2; 80,22</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,48</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,97</t>
+          <t>-0,85; 0,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,55</t>
+          <t>-1,1; 0,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,08</t>
+          <t>-1,53; 0,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,04</t>
+          <t>-1,48; 0,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,39</t>
+          <t>-1,29; 0,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,97</t>
+          <t>-0,75; 1,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,56</t>
+          <t>-0,84; 0,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,38</t>
+          <t>-1,06; 0,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,16</t>
+          <t>-0,96; 0,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-36,23%</t>
+          <t>-36,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,06%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,94%</t>
+          <t>-21,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 64,52</t>
+          <t>-35,74; 64,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 37,38</t>
+          <t>-46,84; 41,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 8,05</t>
+          <t>-65,41; 6,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,34</t>
+          <t>-100,0; 37,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-84,19; 148,3</t>
+          <t>-85,09; 105,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,62; 194,98</t>
+          <t>-60,51; 317,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 45,53</t>
+          <t>-42,54; 37,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 34,5</t>
+          <t>-51,88; 23,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 11,53</t>
+          <t>-51,21; 26,9</t>
         </is>
       </c>
     </row>
